--- a/data/trans_orig/IP28_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84096</t>
+          <t>84082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>79176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85561</t>
+          <t>85573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166421</t>
+          <t>166497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173799</t>
+          <t>174269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401187</t>
+          <t>400399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408707</t>
+          <t>408738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461120</t>
+          <t>461371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469172</t>
+          <t>469148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>865881</t>
+          <t>866014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>876193</t>
+          <t>876945</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>163569</t>
+          <t>164767</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153613</t>
+          <t>152972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320948</t>
+          <t>320638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24919</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>655049</t>
+          <t>655994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665664</t>
+          <t>665588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>700419</t>
+          <t>700192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710170</t>
+          <t>709875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1360485</t>
+          <t>1360445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1373944</t>
+          <t>1374091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76006</t>
+          <t>75855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81801</t>
+          <t>81792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71207</t>
+          <t>71779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149312</t>
+          <t>150011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156779</t>
+          <t>156815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23936</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393977</t>
+          <t>394910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404835</t>
+          <t>404818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>435598</t>
+          <t>435549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445310</t>
+          <t>445244</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>834995</t>
+          <t>834915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>847870</t>
+          <t>847928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148887</t>
+          <t>149613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157787</t>
+          <t>157952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163048</t>
+          <t>163042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309535</t>
+          <t>310020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316512</t>
+          <t>316522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33541</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626303</t>
+          <t>626836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638830</t>
+          <t>638084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>670546</t>
+          <t>670673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681918</t>
+          <t>681548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301504</t>
+          <t>1300997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1317863</t>
+          <t>1317728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46350</t>
+          <t>46785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56255</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105547</t>
+          <t>105659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110633</t>
+          <t>110637</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417463</t>
+          <t>417319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>424011</t>
+          <t>424052</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>427938</t>
+          <t>427811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>435405</t>
+          <t>435394</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>847713</t>
+          <t>848570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>858068</t>
+          <t>858248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152683</t>
+          <t>152863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166020</t>
+          <t>165658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320819</t>
+          <t>320861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325521</t>
+          <t>325516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>621744</t>
+          <t>622033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>630026</t>
+          <t>630001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655961</t>
+          <t>655726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664147</t>
+          <t>664136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1280921</t>
+          <t>1280509</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1292547</t>
+          <t>1292470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57117</t>
+          <t>56836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>112234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14406</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443111</t>
+          <t>442588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>453145</t>
+          <t>453412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>503566</t>
+          <t>504166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512398</t>
+          <t>512583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951297</t>
+          <t>950415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963935</t>
+          <t>963554</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143716</t>
+          <t>143883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177597</t>
+          <t>177661</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324713</t>
+          <t>324409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330730</t>
+          <t>330738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25321</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>644357</t>
+          <t>644039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>656132</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744770</t>
+          <t>745024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754838</t>
+          <t>754818</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1394443</t>
+          <t>1393469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1408923</t>
+          <t>1409248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP28_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP28_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2764</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7097</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1628</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5420</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5556</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2764</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7070</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83482</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>79149</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>85437</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87874</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>84082</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>83946</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>89502</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,79%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83482</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79176</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>85573</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,8%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>257</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166497</t>
+          <t>166642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174269</t>
+          <t>173949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86246</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86246</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86246</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>89502</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>89502</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>89502</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86246</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86246</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86246</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2578</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10751</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5823</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11140</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2781</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10522</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5408</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2681</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10458</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17354</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>466421</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>461078</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>469251</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>405716</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>400399</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>408738</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>401017</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>408758</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,32%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>466421</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>461371</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>469148</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1315</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>866014</t>
+          <t>865545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>876945</t>
+          <t>876536</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>471829</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>471829</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>471829</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>621</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>411539</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>411539</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>411539</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>471829</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>471829</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>471829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2934</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1380</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4705</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4895</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3844</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156177</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153882</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156816</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>168092</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>164767</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>164577</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>169472</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,11%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156177</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>152972</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156816</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>478</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320638</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325650</t>
+          <t>325652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156816</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156816</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156816</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169472</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169472</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169472</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156816</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156816</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156816</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,69 +1757,69 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15615</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14519</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4603</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14566</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>2,17%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14699</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>26</t>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24959</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>706081</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>699276</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>709966</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>989</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>661681</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>655994</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>665588</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>655947</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>665910</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>97,83%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>706081</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>700192</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>709875</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1360445</t>
+          <t>1359362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1374091</t>
+          <t>1373715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>714891</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>714891</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>714891</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>670513</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>670513</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>670513</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>714891</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>714891</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>714891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5018</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2795</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6696</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6951</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3857</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74388</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70618</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75636</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>79756</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>75855</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>75600</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>81792</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,08%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>74388</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71779</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>75636</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,9%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>221</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150011</t>
+          <t>149453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156815</t>
+          <t>156772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75636</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75636</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75636</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>82551</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>82551</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>82551</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75636</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75636</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75636</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2674,67 +2674,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>8063</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4366</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13677</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>8742</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14665</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4620</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14547</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8063</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13807</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24016</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>441293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>435679</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>444990</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>581</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>400833</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>394910</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>404818</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>395028</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>404955</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,87%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>441293</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>435549</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>445244</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>834915</t>
+          <t>834279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>847928</t>
+          <t>848049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>449356</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>449356</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>449356</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>593</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>409575</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>409575</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>409575</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>449356</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>449356</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>449356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5967</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1514</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4618</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5744</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161588</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157729</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163044</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152717</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149613</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148880</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154231</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161588</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>157952</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>163042</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>447</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310020</t>
+          <t>308777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316522</t>
+          <t>316508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163696</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163696</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163696</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154231</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154231</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154231</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163696</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163696</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6869</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18014</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13052</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8273</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19521</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7493</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19592</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7140</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18015</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>17427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>967</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>677269</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>670674</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>681819</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>633305</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>626836</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>638084</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>626765</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>638864</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>967</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>677269</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>670673</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>681548</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1300997</t>
+          <t>1301677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1317728</t>
+          <t>1317618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>688688</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>688688</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>688688</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>646357</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>646357</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>646357</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>688688</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>688688</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>688688</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4144</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3664</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3784</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4662</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>59488</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56670</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60814</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>49696</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46785</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46665</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>50449</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,5%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>59488</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60814</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>161</t>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105659</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110637</t>
+          <t>110635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60814</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60814</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60814</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>50449</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>50449</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>50449</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60814</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60814</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60814</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4277,67 +4277,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8823</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>4276</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1759</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8492</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1786</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9458</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4710</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>432696</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>428583</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>435403</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>421535</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>417319</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>424052</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>416353</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>424025</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>432696</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>427811</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>435394</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>848570</t>
+          <t>847836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>858248</t>
+          <t>858068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>437406</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>437406</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>437406</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>644</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>425811</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>425811</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>425811</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>437406</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>437406</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>437406</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3623</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1343</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4099</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4698</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>168552</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>165555</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>169178</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155619</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152863</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>152264</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>156962</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>168552</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>165658</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>169178</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>320861</t>
+          <t>320783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325516</t>
+          <t>325513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>169178</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>169178</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>169178</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156962</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156962</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156962</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>169178</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>169178</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169178</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4963,97 +4963,97 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11530</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>6372</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11189</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11453</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11672</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>8009</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>20213</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>13033</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>20111</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5071,99 +5071,99 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>660737</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>655868</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>663520</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>944</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>626850</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>622033</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>630001</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>621769</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>630109</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>660737</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>655726</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>664136</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1287587</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1280407</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1292611</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>99,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1287587</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1280509</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1292470</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>98,45%</t>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>667398</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>633222</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>633222</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>633222</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>667398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5859</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5168</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4896</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4448</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50873</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60658</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56836</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>150</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115336</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112234</t>
+          <t>98594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10051</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7830</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3582</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14406</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>468805</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>463625</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>471614</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>629</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>449164</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>442588</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>453412</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>509336</t>
+          <t>420325</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504166</t>
+          <t>413399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512583</t>
+          <t>424232</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>958499</t>
+          <t>889130</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950415</t>
+          <t>881074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963554</t>
+          <t>894139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>473676</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>473676</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>473676</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>456994</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>456994</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>456994</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514582</t>
+          <t>428736</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514582</t>
+          <t>428736</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514582</t>
+          <t>428736</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>971576</t>
+          <t>902412</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>971576</t>
+          <t>902412</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>971576</t>
+          <t>902412</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4791</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5668</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4294</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166030</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162080</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166871</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>147839</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143883</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>148153</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>144105</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>181095</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>177661</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>181955</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>463</t>
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>328934</t>
+          <t>314183</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324409</t>
+          <t>309273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>330738</t>
+          <t>316049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166871</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166871</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166871</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181955</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181955</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181955</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>331506</t>
+          <t>316848</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>331506</t>
+          <t>316848</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>331506</t>
+          <t>316848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12623</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>26670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>690247</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>684657</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>693647</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>651681</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>644039</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>656302</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>751088</t>
+          <t>615236</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>745024</t>
+          <t>607203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754818</t>
+          <t>620004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1402769</t>
+          <t>1305482</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1393469</t>
+          <t>1296080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1409248</t>
+          <t>1312098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>697280</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>661223</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>661223</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>661223</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625470</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625470</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>758541</t>
+          <t>625470</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1419764</t>
+          <t>1322750</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1419764</t>
+          <t>1322750</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1419764</t>
+          <t>1322750</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
